--- a/Backend/app/zavoz/exelfiles/файл_товары_14.xlsx
+++ b/Backend/app/zavoz/exelfiles/файл_товары_14.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vs code\Sofia_tech\Backend\app\zavoz\exelfiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{55CEDE78-ECD5-40EE-833D-56DF02806775}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D900609-FE38-4B56-AD19-6A8F0D92E221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{29E1083E-1BB7-40DC-91C7-D7EDB4B75F74}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2414" uniqueCount="1216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2415" uniqueCount="1217">
   <si>
     <t>Actual code</t>
   </si>
@@ -3688,6 +3688,9 @@
   </si>
   <si>
     <t>Изображение</t>
+  </si>
+  <si>
+    <t>Price</t>
   </si>
 </sst>
 </file>
@@ -4941,7 +4944,9 @@
       <c r="I1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="17"/>
+      <c r="J1" s="17" t="s">
+        <v>1216</v>
+      </c>
     </row>
     <row r="2" spans="1:10" ht="17.100000000000001" customHeight="1">
       <c r="A2" s="1">
@@ -4978,7 +4983,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="20">
-        <v>22</v>
+        <v>225</v>
       </c>
       <c r="C3" s="1">
         <v>14</v>
@@ -5008,7 +5013,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="20">
-        <v>22</v>
+        <v>225</v>
       </c>
       <c r="C4" s="1">
         <v>14</v>
@@ -19399,19 +19404,19 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<unk8:FormTemplates xmlns:unk8="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <unk8:Display>DocumentLibraryForm</unk8:Display>
+  <unk8:Edit>DocumentLibraryForm</unk8:Edit>
+  <unk8:New>DocumentLibraryForm</unk8:New>
+</unk8:FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <unk9:properties xmlns:unk9="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:unk6="8729324c-9082-48e6-8b1f-a02697143159">
   <documentManagement>
     <unk6:_activity xsi:nil="true"/>
   </documentManagement>
 </unk9:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<unk8:FormTemplates xmlns:unk8="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <unk8:Display>DocumentLibraryForm</unk8:Display>
-  <unk8:Edit>DocumentLibraryForm</unk8:Edit>
-  <unk8:New>DocumentLibraryForm</unk8:New>
-</unk8:FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19660,6 +19665,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F7D4337-2590-43DE-9DBE-C469D04EFAAF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{945B434C-0DED-439B-BC32-FF1F889F3B0A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
@@ -19672,14 +19685,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F7D4337-2590-43DE-9DBE-C469D04EFAAF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
